--- a/outputs/operations/План_действий_2026-09.xlsx
+++ b/outputs/operations/План_действий_2026-09.xlsx
@@ -2384,7 +2384,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Закупить стеллажи на 100 кв. м</t>
+          <t>Решить, нужен ли второй контейнер под светильники и электрику</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>без них 100 кв. м не хватит</t>
+          <t>в 100 кв. м без стеллажей они не помещаются</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Расчет показывает потребность 150-170 кв. м вместо 100. Дефицит закрывается продажей насосов и сепараторов, вторым контейнером под светильники и стеллажами.</t>
+          <t>Себе оставляем 100 кв. м без стеллажей. В них помещается только крупногабарит, и то впритык: по оценке он занимает 105-120 кв. м. Все остальное уходит в контейнеры или продается.</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Продать лотом</t>
+          <t>В контейнер</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -4525,14 +4525,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>или в 20-футовый, 25-30 кв. м</t>
+          <t>в 20-футовый, легкие и объемные</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Оставить в 100 кв. м</t>
+          <t>В контейнер</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -4551,14 +4551,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>на стеллажи, около 10 кв. м</t>
+          <t>компактная, идет в ящиках</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Оставить в 100 кв. м</t>
+          <t>В контейнер</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -4580,7 +4580,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Оставить в 100 кв. м</t>
+          <t>В контейнер</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -4619,7 +4619,11 @@
       <c r="E18" s="16" t="n">
         <v>972500</v>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>крупногабарит</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4674,7 +4678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4808,12 +4812,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Бюджет на стеллажи в 100 кв. м</t>
+          <t>Нужен ли второй контейнер</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Без стеллажей товар в 100 кв. м не помещается</t>
+          <t>Решено оставить себе ровно 100 кв. м без стеллажей. В них помещается только крупногабарит, все остальное уходит в контейнеры</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4829,12 +4833,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Процент сотруднице с продаж за две недели</t>
+          <t>Кто платит за охрану общей территории</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Иначе нет причин дожимать сделки перед уходом</t>
+          <t>Сторож охраняет и часть арендатора, 38 400 руб в месяц</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -4844,172 +4848,130 @@
       </c>
       <c r="E9" s="19" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Оставляем 100 кв. м или 130-150 кв. м</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Решается после обмера: расчет показывает нехватку 50-70 кв. м</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Кто платит за охрану общей территории</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Сторож охраняет и часть арендатора, 38 400 руб в месяц</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Риски</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Риск</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Что делаем</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Риски</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Риск</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Что делаем</t>
+      <c r="A13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Не нашли администратора за неделю</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Она передает дела напрямую в Москву без второй недели обучения, показания за сентябрь снимает сама, работы с подрядчиками переносятся. Договориться о платной телефонной консультации на месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Сдали в металл то, что стоит денег</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Двери и крышки в наличии стоят 4 080 000 руб, среди них крышка цилиндра Пилстик за 550 000. Список на металл подписывает Олеся, сверяя с реестром</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Не нашли администратора за неделю</t>
+          <t>Товар не помещается в 100 кв. м</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Она передает дела напрямую в Москву без второй недели обучения, показания за сентябрь снимает сама, работы с подрядчиками переносятся. Договориться о платной телефонной консультации на месяц</t>
+          <t>Решено: 100 кв. м без стеллажей. В них идет только крупногабарит, около 105-120 кв. м по оценке. Значит светильники и мелкая электрика уходят в контейнеры, а часть насосов и сепараторов надо продать или вынести под тент</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Сдали в металл то, что стоит денег</t>
+          <t>Объект без ответственного</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Двери и крышки в наличии стоят 4 080 000 руб, среди них крышка цилиндра Пилстик за 550 000. Список на металл подписывает Олеся, сверяя с реестром</t>
+          <t>Пока администратора нет, сторож единственный человек на площадке с товаром на 93 млн. Задачи ему ставит Москва напрямую, ежедневное фото территории</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Товар не помещается в 100 кв. м</t>
+          <t>Продажа тянется, аренда не начинается</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Расчет показывает потребность 150-170 кв. м. Закрывается продажей насосов и сепараторов, вторым контейнером под светильники и стеллажами</t>
+          <t>Отсечка касается здания, а не товара: к дате все вывозится в контейнер, здание сдается, продажа продолжается</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Объект без ответственного</t>
+          <t>Перегруз и просадка контейнера</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Пока администратора нет, сторож единственный человек на площадке с товаром на 93 млн. Задачи ему ставит Москва напрямую, ежедневное фото территории</t>
+          <t>Контейнер стационарный, поэтому вес не ограничен транспортной нормой, но нужно твердое основание, поддоны под тяжелое и распределение по длине</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Продажа тянется, аренда не начинается</t>
+          <t>Потеря контактов покупателей</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Отсечка касается здания, а не товара: к дате все вывозится в контейнер, здание сдается, продажа продолжается</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Перегруз и просадка контейнера</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Контейнер стационарный, поэтому вес не ограничен транспортной нормой, но нужно твердое основание, поддоны под тяжелое и распределение по длине</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Потеря контактов покупателей</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Журнал обзвона на 40+ компаний уходит вместе с сотрудницей. Передать Олесе со статусами, а не список телефонов</t>
         </is>

--- a/outputs/operations/План_действий_2026-09.xlsx
+++ b/outputs/operations/План_действий_2026-09.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Решения и риски" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Передача дел'!$A$4:$F$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Склад и здание'!$A$4:$F$19</definedName>
   </definedNames>
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Решить, нужен ли второй контейнер под светильники и электрику</t>
+          <t>Полностью освободить здание: товара внутри не остается</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>в 100 кв. м без стеллажей они не помещаются</t>
+          <t>500 кв. м аренда, 100 кв. м мастерская</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
+          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>2844 единицы, опись обязательна</t>
+          <t>45-55 куб. м, на поддоны, не на землю</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Маркировать ящики и поддоны по строкам реестра</t>
+          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>иначе не найти проданную позицию</t>
+          <t>кран-балка есть на улице, не продавать</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Освободить гараж от мусора</t>
+          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2517,7 +2517,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>часть аренды можно закрывать ремонтом брака</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="n">
@@ -2540,7 +2544,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Перенести насосы из фойе после маркировки и фото</t>
+          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2555,7 +2559,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>6 910 000 руб, сначала бирки</t>
+          <t>2844 единицы, опись обязательна</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2584,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Покраска будки сторожей</t>
+          <t>Маркировать ящики и поддоны по строкам реестра</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -2593,7 +2597,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>иначе не найти проданную позицию</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -2616,12 +2624,12 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
+          <t>Освободить гараж от мусора</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2629,11 +2637,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>иначе будете платить за арендатора</t>
-        </is>
-      </c>
+      <c r="H56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -2656,12 +2660,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
+          <t>Перенести насосы из фойе после маркировки и фото</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2671,7 +2675,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>приложение к договору аренды</t>
+          <t>6 910 000 руб, сначала бирки</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
+          <t>Покраска будки сторожей</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2732,7 +2736,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Переговоры с Валентином и выход на рынок аренды</t>
+          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2747,7 +2751,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>не завязываться на одного арендатора</t>
+          <t>иначе будете платить за арендатора</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2771,17 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
+          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2785,7 +2789,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>приложение к договору аренды</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -2803,17 +2811,17 @@
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
+          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -2839,17 +2847,17 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Работа по откликам, отгрузки</t>
+          <t>Переговоры с Валентином и выход на рынок аренды</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -2857,7 +2865,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>не завязываться на одного арендатора</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -2880,7 +2892,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2893,11 +2905,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>15,9 млн и 76 кв. м площади</t>
-        </is>
-      </c>
+      <c r="H63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -2920,7 +2928,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Составить список на металл и сверить с реестром</t>
+          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -2933,11 +2941,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>только брак и хлам, подписывает Олеся</t>
-        </is>
-      </c>
+      <c r="H64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -2960,140 +2964,140 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
+          <t>Работа по откликам, отгрузки</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>15,9 млн и 76 кв. м площади</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Составить список на металл и сверить с реестром</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>только брак и хлам, подписывает Олеся</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
           <t>Запросить цены в 2-3 приемках металла отдельно по цветному</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>бронза дороже черного в разы</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>Передать показания света: Калинина, Светланская, Фокино</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>ДЭК 18112 и 7182</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>20-25 числа</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>Передать показания воды по четырем объектам</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Водоканал 1008</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>20-25 числа</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>Оплатить воду по четырем объектам</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="n">
@@ -3106,7 +3110,7 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>по счету</t>
+          <t>ежемесячно</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -3116,12 +3120,12 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Оплатить свет</t>
+          <t>Передать показания света: Калинина, Светланская, Фокино</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -3129,7 +3133,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>ДЭК 18112 и 7182</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="n">
@@ -3142,7 +3150,7 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>ежемесячно</t>
+          <t>20-25 числа</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -3152,7 +3160,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Принять и оплатить смены сторожей</t>
+          <t>Передать показания воды по четырем объектам</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -3167,7 +3175,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>1280 руб за сутки</t>
+          <t>Водоканал 1008</t>
         </is>
       </c>
     </row>
@@ -3182,110 +3190,222 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
+          <t>20-25 числа</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Оплатить воду по четырем объектам</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>по счету</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Оплатить свет</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Принять и оплатить смены сторожей</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>1280 руб за сутки</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
           <t>еженедельно</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>Обход объектов, фотоотчет</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>способ контроля на удаленке</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="D73" s="11" t="inlineStr">
+    <row r="76">
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>Сводка</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>Всего задач</t>
         </is>
       </c>
-      <c r="F73" s="12">
-        <f>COUNTA(E5:E71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="F74" s="12">
-        <f>COUNTIF(G5:G71,"Не начато")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="F75" s="12">
-        <f>COUNTIF(G5:G71,"В работе")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Сделано</t>
-        </is>
-      </c>
       <c r="F76" s="12">
-        <f>COUNTIF(G5:G71,"Сделано")</f>
+        <f>COUNTA(E5:E74)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Отменено</t>
+          <t>Не начато</t>
         </is>
       </c>
       <c r="F77" s="12">
-        <f>COUNTIF(G5:G71,"Отменено")</f>
+        <f>COUNTIF(G5:G74,"Не начато")</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="E78" s="12" t="inlineStr">
         <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="F78" s="12">
+        <f>COUNTIF(G5:G74,"В работе")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Сделано</t>
+        </is>
+      </c>
+      <c r="F79" s="12">
+        <f>COUNTIF(G5:G74,"Сделано")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Отменено</t>
+        </is>
+      </c>
+      <c r="F80" s="12">
+        <f>COUNTIF(G5:G74,"Отменено")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="E81" s="12" t="inlineStr">
+        <is>
           <t>Готовность</t>
         </is>
       </c>
-      <c r="F78" s="13">
-        <f>IFERROR(F76/F73,0)</f>
+      <c r="F81" s="13">
+        <f>IFERROR(F79/F76,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H71"/>
+  <autoFilter ref="A4:H74"/>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Сделано,Отменено"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4226,14 +4346,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Здание 600 кв. м: 500 в аренду, 100 себе</t>
+          <t>Здание 600 кв. м: 500 в аренду, 100 под мастерскую</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себе оставляем 100 кв. м без стеллажей. В них помещается только крупногабарит, и то впритык: по оценке он занимает 105-120 кв. м. Все остальное уходит в контейнеры или продается.</t>
+          <t>100 кв. м уходят под ремонт арматуры и насосов, товара в здании не остается. Вывезти надо все: 10 635 единиц, 155-190 куб. м. В два контейнера влезает 100 куб. м, разрыв закрывают продажа светильников лотом и навес во дворе под крупногабарит.</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4392,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>В контейнер</t>
+          <t>В 40-фут контейнер</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -4291,92 +4411,88 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>40-футовый, покупается</t>
+          <t>30-38 куб. м</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>В контейнер</t>
+          <t>В 40-фут контейнер</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ЗИП двигателей и насосов</t>
+          <t>Электрика: автоматы, контакторы, реле, приборы, лампы</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>57</v>
+        <v>2971</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>2060280</v>
+        <v>5942388</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>туда же, места хватит</t>
+          <t>компактная, в ящиках</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>В 40-фут контейнер</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Насосы</t>
+          <t>ЗИП двигателей и насосов</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>10654468</v>
+        <v>2060280</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>около 50 кв. м, спрос подтвержден</t>
+          <t>дорогой и мелкий</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>В 40-фут контейнер</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Сепараторы и барабаны</t>
+          <t>Головки, грибки, компенсаторы</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>3520000</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>около 20 кв. м, просили с Камчатки</t>
-        </is>
-      </c>
+        <v>1026000</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>В 40-фут контейнер</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -4395,14 +4511,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>спрос Владивосток и Камчатка</t>
+          <t>4-6 куб. м, на поддоны</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>В 20-фут контейнер</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -4421,40 +4537,36 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>не в металл, стоят денег</t>
+          <t>на ребро, 8-12 куб. м</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>В 20-фут контейнер</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Камбузное оборудование, плиты</t>
+          <t>Блокформы и балласт</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>1710000</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>по 460 кг штука</t>
-        </is>
-      </c>
+        <v>1276000</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>В 20-фут контейнер</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -4473,179 +4585,187 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>спрос подтвержден</t>
+          <t>тяжелые, на поддоны</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Продать</t>
+          <t>Продать лотом</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Регулятор РТНД-150</t>
+          <t>Светильники и комплектующие</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3</v>
+        <v>4512</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>3450000</v>
+        <v>6588412</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>сначала проверить наличие</t>
+          <t>50-60 куб. м, треть всего объема</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>В контейнер</t>
+          <t>Продать или под навес</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Светильники и комплектующие</t>
+          <t>Насосы</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4512</v>
+        <v>85</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>6588412</v>
+        <v>10654468</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>в 20-футовый, легкие и объемные</t>
+          <t>25-35 куб. м, сталь, зимует под тентом</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>В контейнер</t>
+          <t>Продать или под навес</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Электрика: автоматы, контакторы, реле, приборы</t>
+          <t>Сепараторы и барабаны</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>122</v>
+        <v>8</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1195</v>
+        <v>16</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>5809013</v>
+        <v>3520000</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>компактная, идет в ящиках</t>
+          <t>12-18 куб. м</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>В контейнер</t>
+          <t>Продать или под навес</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Головки, грибки, компенсаторы</t>
+          <t>Камбузное оборудование, плиты</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>1026000</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
+        <v>1710000</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>по 460 кг штука</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>В контейнер</t>
+          <t>Продать</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Блокформы и балласт</t>
+          <t>Регулятор РТНД-150</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>116</v>
+        <v>3</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr"/>
+        <v>3450000</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>сначала проверить наличие</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Оставить в 100 кв. м</t>
+          <t>Продать</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Компрессоры и приводы</t>
+          <t>Компрессоры, приводы, такелаж, прочее</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5</v>
+        <v>210</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>972500</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>крупногабарит</t>
-        </is>
-      </c>
+        <v>2147215</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Оставить в 100 кв. м</t>
+          <t>В мастерскую на ремонт</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Такелаж, крышки, прочее</t>
+          <t>Брак и некомплект: клапаны, задвижки, сепараторы</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>205</v>
+        <v>50</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>1174715</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr"/>
+        <v>2372500</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>после ремонта цена выше</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="11" t="inlineStr">
@@ -4678,7 +4798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4812,12 +4932,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Нужен ли второй контейнер</t>
+          <t>Мастерская своя или сдаем в аренду</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Решено оставить себе ровно 100 кв. м без стеллажей. В них помещается только крупногабарит, все остальное уходит в контейнеры</t>
+          <t>100 кв. м под ремонт арматуры и насосов. Первый кандидат в арендаторы — мастер, который уже приходит ремонтировать нашу арматуру</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -4833,145 +4953,202 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>Хватит ли электрической мощности на мастерскую</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Станки требуют 380 В. Проверить, сколько выделено на здание и что останется после раздела с арендатором</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Ставим ли навес во дворе под крупногабарит</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Насосы, сепараторы и плиты — 45-55 куб. м. В контейнеры вместе со всем остальным не влезают</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>Кто платит за охрану общей территории</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Сторож охраняет и часть арендатора, 38 400 руб в месяц</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Риски</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Что делаем</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Не нашли администратора за неделю</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Она передает дела напрямую в Москву без второй недели обучения, показания за сентябрь снимает сама, работы с подрядчиками переносятся. Договориться о платной телефонной консультации на месяц</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Сдали в металл то, что стоит денег</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Двери и крышки в наличии стоят 4 080 000 руб, среди них крышка цилиндра Пилстик за 550 000. Список на металл подписывает Олеся, сверяя с реестром</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Товар не помещается в 100 кв. м</t>
+          <t>Не нашли администратора за неделю</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Решено: 100 кв. м без стеллажей. В них идет только крупногабарит, около 105-120 кв. м по оценке. Значит светильники и мелкая электрика уходят в контейнеры, а часть насосов и сепараторов надо продать или вынести под тент</t>
+          <t>Она передает дела напрямую в Москву без второй недели обучения, показания за сентябрь снимает сама, работы с подрядчиками переносятся. Договориться о платной телефонной консультации на месяц</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Объект без ответственного</t>
+          <t>Сдали в металл то, что стоит денег</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Пока администратора нет, сторож единственный человек на площадке с товаром на 93 млн. Задачи ему ставит Москва напрямую, ежедневное фото территории</t>
+          <t>Двери и крышки в наличии стоят 4 080 000 руб, среди них крышка цилиндра Пилстик за 550 000. Список на металл подписывает Олеся, сверяя с реестром</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Продажа тянется, аренда не начинается</t>
+          <t>Товар не помещается в два контейнера</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Отсечка касается здания, а не товара: к дате все вывозится в контейнер, здание сдается, продажа продолжается</t>
+          <t>Весь товар из здания — 155-190 куб. м, а 40-футовый и 20-футовый вместе дают 100 куб. м. Разрыв закрывают продажа светильников лотом (50-60 куб. м) и навес во дворе под насосы, сепараторы и плиты (45-55 куб. м). Третий контейнер покупать не надо</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Перегруз и просадка контейнера</t>
+          <t>Мастерская мешает арендатору 500 кв. м</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Контейнер стационарный, поэтому вес не ограничен транспортной нормой, но нужно твердое основание, поддоны под тяжелое и распределение по длине</t>
+          <t>Сварка, шлифовка и шум рядом с чужим арендатором — источник конфликта. Обсудить до подписания договора, а не после</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Объект без ответственного</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Пока администратора нет, сторож единственный человек на площадке с товаром на 93 млн. Задачи ему ставит Москва напрямую, ежедневное фото территории</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Продажа тянется, аренда не начинается</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Отсечка касается здания, а не товара: к дате все вывозится в контейнер, здание сдается, продажа продолжается</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Перегруз и просадка контейнера</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Контейнер стационарный, поэтому вес не ограничен транспортной нормой, но нужно твердое основание, поддоны под тяжелое и распределение по длине</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Потеря контактов покупателей</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Журнал обзвона на 40+ компаний уходит вместе с сотрудницей. Передать Олесе со статусами, а не список телефонов</t>
         </is>

--- a/outputs/operations/План_действий_2026-09.xlsx
+++ b/outputs/operations/План_действий_2026-09.xlsx
@@ -8,14 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="План действий" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Передача дел" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Склад и здание" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Решения и риски" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Успеть до 23 сентября" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Итоги по складу" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Передача дел" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Склад и здание" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Решения и риски" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Кто нужен в команду" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Передача дел'!$A$4:$F$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Склад и здание'!$A$4:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Успеть до 23 сентября'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Передача дел'!$A$4:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Склад и здание'!$A$4:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,12 +66,17 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -134,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,10 +174,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -542,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1452,7 +1467,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Проставить цены на 100 позиций без цены</t>
+          <t>Оценить ЗИП двигателей: Пилстик 6ЧН40/46, VD26/20, 6NVD26 А3</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1467,7 +1482,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>начать с тех, что нужны для КП</t>
+          <t>249 позиций без цены, самое дорогое из неоцененного</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1507,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Свести к одной цене 10 наименований с разной ценой</t>
+          <t>Проставить цены на остальные позиции без цены</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -1505,7 +1520,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>начать с тех, что нужны для КП</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1518,106 +1537,110 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>10-14 сен</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Спросить мастера: взаимозаменяемы ли VD26/20 и 6NVD26 А3</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>одна серия SKL 260/200, тогда это один лот</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Неделя 1</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>10-14 сен</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Свести к одной цене 10 наименований с разной ценой</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Неделя 1</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
           <t>13-16 сен</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Разобрать фотоархив по позициям</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Олеся</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>папка Фото на Google Drive</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Неделя 2</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>сотрудница + новый</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Неделя 2</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Обход Светланской, Фокино, Аксаковской</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>сотрудница + новый</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
@@ -1640,7 +1663,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -1653,11 +1676,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>смена 1280 руб</t>
-        </is>
-      </c>
+      <c r="H31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
@@ -1680,7 +1699,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+          <t>Обход Светланской, Фокино, Аксаковской</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -1693,11 +1712,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>включая мастера по ремонту арматуры</t>
-        </is>
-      </c>
+      <c r="H32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
@@ -1710,7 +1725,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>20-25 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1720,12 +1735,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Новый сам снимает и передает показания по всем объектам</t>
+          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + новый</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -1735,7 +1750,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>контрольная точка, она рядом и проверяет</t>
+          <t>смена 1280 руб</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1765,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>20-25 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1760,12 +1775,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Новый сам оплачивает воду по четырем объектам</t>
+          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + новый</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -1773,7 +1788,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>включая мастера по ремонту арматуры</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
@@ -1786,7 +1805,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>22 сен</t>
+          <t>20-25 сен</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1796,7 +1815,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Контрольный день: новый работает один</t>
+          <t>Новый сам снимает и передает показания по всем объектам</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -1811,7 +1830,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>она на телефоне</t>
+          <t>контрольная точка, она рядом и проверяет</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1845,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>23 сен</t>
+          <t>20-25 сен</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1836,12 +1855,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Акт приема-передачи, отзыв ключей, смена паролей</t>
+          <t>Новый сам оплачивает воду по четырем объектам</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1862,22 +1881,22 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>22 сен</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Выложить на Авито и Фарпост первую волну: 24 объявления</t>
+          <t>Контрольный день: новый работает один</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -1887,7 +1906,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>позиции дороже 500 тыс</t>
+          <t>она на телефоне</t>
         </is>
       </c>
     </row>
@@ -1902,22 +1921,22 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>23 сен</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Адресные КП тем, кто просил цену и не получил</t>
+          <t>Акт приема-передачи, отзыв ключей, смена паролей</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>сотрудница</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1925,11 +1944,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>камчатский колхоз, НН, Владивосток</t>
-        </is>
-      </c>
+      <c r="H38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
@@ -1952,7 +1967,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Предложение по светильникам СС328 одним лотом</t>
+          <t>Выложить на Авито и Фарпост первую волну: 24 объявления</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1967,7 +1982,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>4512 единиц, главный объем</t>
+          <t>позиции дороже 500 тыс</t>
         </is>
       </c>
     </row>
@@ -1992,12 +2007,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Запрос встречных предложений на склад лотом у 3-5 перекупщиков</t>
+          <t>Адресные КП тем, кто просил цену и не получил</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>сотрудница</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -2007,7 +2022,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>цель — узнать цену рынка</t>
+          <t>камчатский колхоз, НН, Владивосток</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2047,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Выставить на Фарпост баллоны кислородные и станки</t>
+          <t>Предложение по светильникам СС328 одним лотом</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2047,7 +2062,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>их нет в реестре, переписать отдельно</t>
+          <t>4512 единиц, главный объем</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2077,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>20-23 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2072,12 +2087,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
+          <t>Собрать лот ЗИП на Пилстик 6ЧН40/46</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>сотрудница + Олеся</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -2085,7 +2100,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>57 позиций, 1222 единицы, искать судно с этим двигателем</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
@@ -2103,17 +2122,17 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Обмерить, сколько места занимает каждая группа товара</t>
+          <t>Собрать лот ЗИП на VD26/20 и 6NVD26 А3</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>новый + Олеся</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -2123,7 +2142,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>один день с рулеткой и планом</t>
+          <t>28 позиций, 254 единицы</t>
         </is>
       </c>
     </row>
@@ -2143,17 +2162,17 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Узнать рыночную ставку аренды за кв. м в районе</t>
+          <t>Связать ремкомплекты сепараторов с самими сепараторами в КП</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -2163,7 +2182,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>без нее нельзя считать экономику</t>
+          <t>кулачки СЦ-1,5 55 шт, СЦ-3 36 шт, ремкомплекты</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2202,17 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Выбрать и подготовить место под 40-футовый контейнер</t>
+          <t>Запрос встречных предложений на склад лотом у 3-5 перекупщиков</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2203,7 +2222,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>твердое основание, блоки под углы</t>
+          <t>цель — узнать цену рынка</t>
         </is>
       </c>
     </row>
@@ -2223,17 +2242,17 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Воровайка: убрать лебедки с середины двора</t>
+          <t>Выставить на Фарпост баллоны кислородные и станки</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2243,7 +2262,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>чтобы заехал кран</t>
+          <t>их нет в реестре, переписать отдельно</t>
         </is>
       </c>
     </row>
@@ -2258,22 +2277,22 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>20-23 сен</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Вывоз мусора грузовиком с помещения и территории</t>
+          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + Олеся</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2281,11 +2300,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>не сторож по мешку</t>
-        </is>
-      </c>
+      <c r="H47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
@@ -2308,258 +2323,262 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
+          <t>Обмерить, сколько места занимает каждая группа товара</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>новый + Олеся</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>один день с рулеткой и планом</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Включить склад электрики в обмер и в план вывоза</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>локация нашлась позже, 117 позиций, 1783 единицы</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Узнать рыночную ставку аренды за кв. м в районе</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>без нее нельзя считать экономику</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Выбрать и подготовить место под 40-футовый контейнер</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>твердое основание, блоки под углы</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Воровайка: убрать лебедки с середины двора</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>чтобы заехал кран</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Вывоз мусора грузовиком с помещения и территории</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>не сторож по мешку</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Освободить 20-футовый контейнер вдоль стены</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>пойдет под светильники</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Купить и поставить 40-футовый контейнер</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Полностью освободить здание: товара внутри не остается</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>500 кв. м аренда, 100 кв. м мастерская</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>45-55 куб. м, на поддоны, не на землю</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>кран-балка есть на улице, не продавать</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>часть аренды можно закрывать ремонтом брака</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>2844 единицы, опись обязательна</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2603,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Маркировать ящики и поддоны по строкам реестра</t>
+          <t>Купить и поставить 40-футовый контейнер</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2597,11 +2616,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>иначе не найти проданную позицию</t>
-        </is>
-      </c>
+      <c r="H55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="9" t="n">
@@ -2624,7 +2639,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Освободить гараж от мусора</t>
+          <t>Полностью освободить здание: товара внутри не остается</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -2637,7 +2652,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>500 кв. м аренда, 100 кв. м мастерская</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="n">
@@ -2660,7 +2679,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Перенести насосы из фойе после маркировки и фото</t>
+          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -2675,7 +2694,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>6 910 000 руб, сначала бирки</t>
+          <t>45-55 куб. м, на поддоны, не на землю</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2719,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Покраска будки сторожей</t>
+          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2713,7 +2732,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>кран-балка есть на улице, не продавать</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="n">
@@ -2736,7 +2759,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
+          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -2751,7 +2774,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>иначе будете платить за арендатора</t>
+          <t>часть аренды можно закрывать ремонтом брака</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2799,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
+          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2791,7 +2814,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>приложение к договору аренды</t>
+          <t>2844 единицы, опись обязательна</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2839,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
+          <t>Маркировать ящики и поддоны по строкам реестра</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -2829,7 +2852,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>иначе не найти проданную позицию</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="n">
@@ -2852,12 +2879,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Переговоры с Валентином и выход на рынок аренды</t>
+          <t>Освободить гараж от мусора</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -2865,11 +2892,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>не завязываться на одного арендатора</t>
-        </is>
-      </c>
+      <c r="H62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -2887,17 +2910,17 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
+          <t>Перенести насосы из фойе после маркировки и фото</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -2905,7 +2928,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>6 910 000 руб, сначала бирки</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="n">
@@ -2923,17 +2950,17 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
+          <t>Покраска будки сторожей</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -2959,17 +2986,17 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Работа по откликам, отгрузки</t>
+          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -2977,7 +3004,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>иначе будете платить за арендатора</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="n">
@@ -2995,17 +3026,17 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3015,7 +3046,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>15,9 млн и 76 кв. м площади</t>
+          <t>приложение к договору аренды</t>
         </is>
       </c>
     </row>
@@ -3035,17 +3066,17 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Составить список на металл и сверить с реестром</t>
+          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -3053,11 +3084,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>только брак и хлам, подписывает Олеся</t>
-        </is>
-      </c>
+      <c r="H67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -3075,337 +3102,565 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Переговоры с Валентином и выход на рынок аренды</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>не завязываться на одного арендатора</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Работа по откликам, отгрузки</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>15,9 млн и 76 кв. м площади</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Составить список на металл и сверить с реестром</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>только брак и хлам, подписывает Олеся</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>Запросить цены в 2-3 приемках металла отдельно по цветному</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>бронза дороже черного в разы</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>Постоянно</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>ежемесячно</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Передать показания света: Калинина, Светланская, Фокино</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>ДЭК 18112 и 7182</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>Постоянно</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>20-25 числа</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Передать показания воды по четырем объектам</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>Водоканал 1008</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>Постоянно</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>20-25 числа</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>Оплатить воду по четырем объектам</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>Постоянно</t>
         </is>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C78" s="10" t="inlineStr">
         <is>
           <t>по счету</t>
         </is>
       </c>
-      <c r="D72" s="10" t="inlineStr">
+      <c r="D78" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>Оплатить свет</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>Постоянно</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>ежемесячно</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D79" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Принять и оплатить смены сторожей</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>1280 руб за сутки</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>Постоянно</t>
         </is>
       </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>еженедельно</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr">
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Обход объектов, фотоотчет</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>способ контроля на удаленке</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="D76" s="11" t="inlineStr">
+    <row r="82">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>Сводка</t>
         </is>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>Всего задач</t>
         </is>
       </c>
-      <c r="F76" s="12">
-        <f>COUNTA(E5:E74)</f>
+      <c r="F82" s="12">
+        <f>COUNTA(E5:E80)</f>
         <v/>
       </c>
     </row>
-    <row r="77">
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="F77" s="12">
-        <f>COUNTIF(G5:G74,"Не начато")</f>
+    <row r="83">
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F83" s="12">
+        <f>COUNTIF(G5:G80,"Не начато")</f>
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="E78" s="12" t="inlineStr">
+    <row r="84">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="F78" s="12">
-        <f>COUNTIF(G5:G74,"В работе")</f>
+      <c r="F84" s="12">
+        <f>COUNTIF(G5:G80,"В работе")</f>
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="E79" s="12" t="inlineStr">
+    <row r="85">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>Сделано</t>
         </is>
       </c>
-      <c r="F79" s="12">
-        <f>COUNTIF(G5:G74,"Сделано")</f>
+      <c r="F85" s="12">
+        <f>COUNTIF(G5:G80,"Сделано")</f>
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="E80" s="12" t="inlineStr">
+    <row r="86">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>Отменено</t>
         </is>
       </c>
-      <c r="F80" s="12">
-        <f>COUNTIF(G5:G74,"Отменено")</f>
+      <c r="F86" s="12">
+        <f>COUNTIF(G5:G80,"Отменено")</f>
         <v/>
       </c>
     </row>
-    <row r="81">
-      <c r="E81" s="12" t="inlineStr">
+    <row r="87">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Готовность</t>
         </is>
       </c>
-      <c r="F81" s="13">
-        <f>IFERROR(F79/F76,0)</f>
+      <c r="F87" s="13">
+        <f>IFERROR(F85/F82,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H74"/>
+  <autoFilter ref="A4:H80"/>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Сделано,Отменено"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3414,6 +3669,963 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Что нельзя сделать после ее ухода</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Остальные задачи из общего плана продолжатся и после 23 сентября. Здесь только то, что уйдет вместе с человеком.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Срок</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Направление</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>10-12 сен</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Забрать логины и пароли: ДЭК, Водоканал, почта, Фарпост</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>доступы забираем в первые три дня</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>10-12 сен</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Забрать лицевые счета по четырем объектам</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>по Аксаковской л/с в файле пустой</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>11 сен</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Закрыть пробелы: порядок подачи по Светланской, л/с по Аксаковской</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>она сама отметила их в своем файле</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>11-12 сен</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Опись ключей, договоры, сканы, подотчетные деньги</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>кто еще имеет ключи и дубликаты</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>12-13 сен</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Видеообход четырех объектов с описью</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>запись сохранить</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>12-13 сен</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Заполнить реестр контактов по всем вопросам</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>шаблон reestr_kontaktov_shablon.tsv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>13-14 сен</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Передать журнал обзвона и статусы покупателей</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>передает Олесе</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>10-16 сен</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Закуп косметики</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Выяснить открытые заказы: что оплачено и не отгружено</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>это живые деньги, первым делом</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>10-16 сен</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Закуп косметики</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Выяснить заказы в пути: что едет и когда придет</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>10-16 сен</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Закуп косметики</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Список брендов и заводов с условиями, ценами, MOQ</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>10-16 сен</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Закуп косметики</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Контакты: байер, консолидатор, склад в Корее, брокер</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>10-16 сен</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Закуп косметики</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Документы: CPNP, декларации, Честный знак</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Обход Светланской, Фокино, Аксаковской</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>смена 1280 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>включая мастера по ремонту арматуры</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Адресные КП тем, кто просил цену и не получил</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>камчатский колхоз, НН, Владивосток</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>20-23 сен</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Всего</t>
+        </is>
+      </c>
+      <c r="D24" s="12">
+        <f>COUNTA(D5:D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Сделано</t>
+        </is>
+      </c>
+      <c r="D25" s="12">
+        <f>COUNTIF(E5:E22,"Сделано")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Осталось</t>
+        </is>
+      </c>
+      <c r="D26" s="14">
+        <f>D24-D25</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F22"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Не начато,В работе,Сделано,Отменено"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Склад судового оборудования в цифрах</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Данные из реестра, пересобираются скриптом build_marine_registry.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Позиций в наличии</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Единиц хранения</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>13 036</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Стоимость по проставленным ценам</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>92 970 568 руб</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>496 позиций с ценой</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Позиций без цены</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2 413 единиц, оценить</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr"/>
+      <c r="B9" s="16" t="inlineStr"/>
+      <c r="C9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Арматура: клапаны и клинкеты</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>288 поз, 3 034 ед</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>40 912 050 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Насосное и механическое</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>134 поз, 1 108 ед</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>20 657 248 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>181 поз, 7 671 ед</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>12 719 930 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Корпусная часть: иллюминаторы, двери</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>30 поз, 195 ед</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>10 055 000 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Трубопроводная обвязка</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>38 поз, 244 ед</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>4 744 800 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Прочее: плиты, блокформы, такелаж</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>28 поз, 286 ед</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>3 881 540 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr"/>
+      <c r="C16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Где нет цен: склад электрики</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>117 поз, 1 783 ед</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>весь ЗИП двигателей</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Где нет цен: склад 3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>70 поз, 262 ед</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Где нет цен: перечень ЗИП и насосов</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>32 поз, 224 ед</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>покрывает улицу</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Где нет цен: склад 2</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>30 поз, 144 ед</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr"/>
+      <c r="B21" s="16" t="inlineStr"/>
+      <c r="C21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>80% стоимости дают</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>79 позиций</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>их ведем точечно</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Объем всего товара из здания</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>155-190 куб. м</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>оценка, нужен обмер</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Вместимость 40-фут плюс 20-фут</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>около 100 куб. м</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>разрыв закрывают продажи и навес</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3490,7 +4702,7 @@
           <t>Личные кабинеты ДЭК и Водоканала: логины и пароли</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3516,7 +4728,7 @@
           <t>Лицевые счета по четырем объектам, включая Аксаковскую</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3542,7 +4754,7 @@
           <t>Доступ к рабочей почте: ДЭК, Водоканал, таможня, поставщики</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3594,7 +4806,7 @@
           <t>Договоры энергоснабжения и водоснабжения, сканы</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3620,7 +4832,7 @@
           <t>Последние показания и последние оплаты по каждому объекту</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3672,7 +4884,7 @@
           <t>Контакты сторожей, график, порядок оплаты</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3776,7 +4988,7 @@
           <t>Таможенный брокер и перевозчики по обоим контейнерам</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3802,7 +5014,7 @@
           <t>Ключи от помещений, гаража, контейнеров, будки — с описью</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3828,7 +5040,7 @@
           <t>Кто еще имеет ключи, у кого дубликаты</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3854,7 +5066,7 @@
           <t>Подотчетные деньги: остаток и за что платила наличными</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3906,7 +5118,7 @@
           <t>Открытые заказы: что оплачено и не отгружено</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3932,7 +5144,7 @@
           <t>Заказы в пути: что едет и когда придет</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3958,7 +5170,7 @@
           <t>Бренды и заводы: контакты, цены, скидки, минимальная партия</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -3984,7 +5196,7 @@
           <t>Байер, консолидатор, склад в Корее, логистика</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -4036,7 +5248,7 @@
           <t>Сверка взаиморасчетов по каждому поставщику</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -4062,7 +5274,7 @@
           <t>Журнал обзвона со статусами по каждой компании</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -4088,7 +5300,7 @@
           <t>Кому отправлены КП и фото, кто что просил</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -4114,7 +5326,7 @@
           <t>Кто на стадии переговоров прямо сейчас</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -4192,7 +5404,7 @@
           <t>Куда и в какие числа передавать показания, по объектам</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
@@ -4310,7 +5522,7 @@
           <t>Осталось критичных</t>
         </is>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <f>COUNTIFS(D5:D35,"критично",E5:E35,"Нет")</f>
         <v/>
       </c>
@@ -4326,13 +5538,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4353,7 +5565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>100 кв. м уходят под ремонт арматуры и насосов, товара в здании не остается. Вывезти надо все: 10 635 единиц, 155-190 куб. м. В два контейнера влезает 100 куб. м, разрыв закрывают продажа светильников лотом и навес во дворе под крупногабарит.</t>
+          <t>100 кв. м уходят под ремонт арматуры и насосов, товара в здании не остается. После находки склада электрики в наличии 745 позиций и 13 036 единиц, из них 249 позиций без цены. Вывозится все: в контейнеры, под навес во дворе или продается.</t>
         </is>
       </c>
     </row>
@@ -4406,7 +5618,7 @@
       <c r="D5" s="6" t="n">
         <v>2787</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="18" t="n">
         <v>40912050</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -4432,7 +5644,7 @@
       <c r="D6" s="6" t="n">
         <v>2971</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="18" t="n">
         <v>5942388</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4458,7 +5670,7 @@
       <c r="D7" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="18" t="n">
         <v>2060280</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4484,7 +5696,7 @@
       <c r="D8" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="18" t="n">
         <v>1026000</v>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -4506,7 +5718,7 @@
       <c r="D9" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="18" t="n">
         <v>7165000</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -4532,7 +5744,7 @@
       <c r="D10" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="18" t="n">
         <v>2745000</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -4558,7 +5770,7 @@
       <c r="D11" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="18" t="n">
         <v>1276000</v>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -4580,7 +5792,7 @@
       <c r="D12" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="18" t="n">
         <v>3713000</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4606,7 +5818,7 @@
       <c r="D13" s="6" t="n">
         <v>4512</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="18" t="n">
         <v>6588412</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -4632,7 +5844,7 @@
       <c r="D14" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="18" t="n">
         <v>10654468</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -4658,7 +5870,7 @@
       <c r="D15" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="18" t="n">
         <v>3520000</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -4684,7 +5896,7 @@
       <c r="D16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="18" t="n">
         <v>1710000</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -4710,7 +5922,7 @@
       <c r="D17" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="18" t="n">
         <v>3450000</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -4736,7 +5948,7 @@
       <c r="D18" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="18" t="n">
         <v>2147215</v>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -4758,7 +5970,7 @@
       <c r="D19" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="18" t="n">
         <v>2372500</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -4768,31 +5980,135 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Оценить и продать</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ЗИП Пилстик 6ЧН40/46, склад электрики</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1222</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>цены нет, оценить в первую очередь</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Оценить и продать</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>ЗИП VD26/20 и 6NVD26 А3, склад электрики</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>254</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Оценить и продать</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>ЗИП прочих двигателей и насосов, ремкомплекты сепараторов</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>307</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>3D6, 4Ч 8,5/11, 4Ч 10,5/13, ZD 72/48, СЦ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Оценить и продать</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Электрика склада электрики: светильники СС844, СС901А-I</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>цены нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C20" s="17">
-        <f>SUM(C5:C19)</f>
+      <c r="C24" s="19">
+        <f>SUM(C5:C23)</f>
         <v/>
       </c>
-      <c r="D20" s="17">
-        <f>SUM(D5:D19)</f>
+      <c r="D24" s="19">
+        <f>SUM(D5:D23)</f>
         <v/>
       </c>
-      <c r="E20" s="18">
-        <f>SUM(E5:E19)</f>
+      <c r="E24" s="20">
+        <f>SUM(E5:E23)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F19"/>
+  <autoFilter ref="A4:F23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4861,7 +6177,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr"/>
+      <c r="E4" s="21" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -4882,7 +6198,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -4903,7 +6219,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -4924,7 +6240,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -4945,7 +6261,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -4966,7 +6282,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -4987,7 +6303,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -5008,7 +6324,7 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -5157,4 +6473,221 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Состав команды: к обсуждению</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Заготовка для разговора, решения не приняты. Желтые колонки заполняем на встрече.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Функция</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Что делает</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Кто сейчас</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Замечание</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Нужен отдельный человек</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Решение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Судовое оборудование, продажи</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Оценка позиций, КП, Авито и Фарпост, переговоры, отгрузки, документы</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Олеся, Владивосток</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>745 позиций и 249 без цены — вопрос, тянет ли это один человек</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Судовое оборудование, ремонт</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Дефектовка, восстановление брака и некомплекта, сборка сепараторов</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>мастер приходит по вызову</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>кандидат в арендаторы 100 кв. м под мастерскую</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Объекты и хозяйство, Владивосток</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Коммуналка по четырем объектам, сторожа, подрядчики, вывоз, обходы</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>ищем, вакансия открыта</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>выход нужен к 18 сентября, иначе обучать будет некому</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Косметика, закуп в Корее</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Бренды и заводы, цены и минимальные партии, заказы, отгрузки, консолидатор, сертификация</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>вела увольняющаяся сотрудница</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>не привязано к Владивостоку, может вести Москва</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Косметика, продажи в Москве</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Маркетплейсы: карточки, SEO, реклама, поставки на склады, аналитика</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>заполнить</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>по этому направлению состав команды не обсуждали</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Логистика и таможня</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Контейнеры из Кореи, брокер, перевозчики, приемка на складах</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>сейчас два контейнера в работе</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Да,Нет,Совмещаем"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/operations/План_действий_2026-09.xlsx
+++ b/outputs/operations/План_действий_2026-09.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Кто нужен в команду" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Успеть до 23 сентября'!$A$4:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Передача дел'!$A$4:$F$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Склад и здание'!$A$4:$F$23</definedName>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>10-13 сен</t>
+          <t>10-16 сен</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Оценить улицу: брашпили Б3 и Б4, лебедки ЛЭ74, ПУ-130, трал</t>
+          <t>ИНВЕНТАРИЗАЦИЯ: пересчитать 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Олеся + новый</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>брашпили уже спрашивал покупатель, цены нет</t>
+          <t>остатки недостоверны, сверка была 15 месяцев назад</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>10-13 сен</t>
+          <t>10-16 сен</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Проверить три спорные цифры: СУНДУК, иллюминатор Ф300, РТНД-150</t>
+          <t>Завести правило: каждая отгрузка отмечается в тот же день</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>24 млн под вопросом</t>
+          <t>иначе через год остатки снова разойдутся</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10-14 сен</t>
+          <t>10-13 сен</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Оценить ЗИП двигателей: Пилстик 6ЧН40/46, VD26/20, 6NVD26 А3</t>
+          <t>Оценить улицу: брашпили Б3 и Б4, лебедки ЛЭ74, ПУ-130, трал</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>249 позиций без цены, самое дорогое из неоцененного</t>
+          <t>брашпили уже спрашивал покупатель, цены нет</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>10-14 сен</t>
+          <t>10-13 сен</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Проставить цены на остальные позиции без цены</t>
+          <t>Проверить три спорные цифры: СУНДУК, иллюминатор Ф300, РТНД-150</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>начать с тех, что нужны для КП</t>
+          <t>24 млн под вопросом</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Спросить мастера: взаимозаменяемы ли VD26/20 и 6NVD26 А3</t>
+          <t>Оценить ЗИП двигателей: Пилстик 6ЧН40/46, VD26/20, 6NVD26 А3</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>одна серия SKL 260/200, тогда это один лот</t>
+          <t>249 позиций без цены, самое дорогое из неоцененного</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Свести к одной цене 10 наименований с разной ценой</t>
+          <t>Проставить цены на остальные позиции без цены</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -1600,7 +1600,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>начать с тех, что нужны для КП</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1613,106 +1617,110 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
+          <t>10-14 сен</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Спросить мастера: взаимозаменяемы ли VD26/20 и 6NVD26 А3</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>одна серия SKL 260/200, тогда это один лот</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Неделя 1</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>10-14 сен</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Свести к одной цене 10 наименований с разной ценой</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Неделя 1</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
           <t>13-16 сен</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Разобрать фотоархив по позициям</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>Олеся</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>папка Фото на Google Drive</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Неделя 2</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>сотрудница + новый</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Неделя 2</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Обход Светланской, Фокино, Аксаковской</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>сотрудница + новый</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
@@ -1735,7 +1743,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -1748,11 +1756,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>смена 1280 руб</t>
-        </is>
-      </c>
+      <c r="H33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -1775,7 +1779,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+          <t>Обход Светланской, Фокино, Аксаковской</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -1788,11 +1792,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>включая мастера по ремонту арматуры</t>
-        </is>
-      </c>
+      <c r="H34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>20-25 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Новый сам снимает и передает показания по всем объектам</t>
+          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + новый</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>контрольная точка, она рядом и проверяет</t>
+          <t>смена 1280 руб</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>20-25 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Новый сам оплачивает воду по четырем объектам</t>
+          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + новый</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -1868,7 +1868,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>включая мастера по ремонту арматуры</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
@@ -1881,7 +1885,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>22 сен</t>
+          <t>20-25 сен</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1891,7 +1895,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Контрольный день: новый работает один</t>
+          <t>Новый сам снимает и передает показания по всем объектам</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1906,7 +1910,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>она на телефоне</t>
+          <t>контрольная точка, она рядом и проверяет</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1925,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>23 сен</t>
+          <t>20-25 сен</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1931,12 +1935,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Акт приема-передачи, отзыв ключей, смена паролей</t>
+          <t>Новый сам оплачивает воду по четырем объектам</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1957,22 +1961,22 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>22 сен</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Выложить на Авито и Фарпост первую волну: 24 объявления</t>
+          <t>Контрольный день: новый работает один</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -1982,7 +1986,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>позиции дороже 500 тыс</t>
+          <t>она на телефоне</t>
         </is>
       </c>
     </row>
@@ -1997,22 +2001,22 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>23 сен</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Адресные КП тем, кто просил цену и не получил</t>
+          <t>Акт приема-передачи, отзыв ключей, смена паролей</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>сотрудница</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -2020,11 +2024,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>камчатский колхоз, НН, Владивосток</t>
-        </is>
-      </c>
+      <c r="H40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Предложение по светильникам СС328 одним лотом</t>
+          <t>Выложить на Авито и Фарпост первую волну: 24 объявления</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>4512 единиц, главный объем</t>
+          <t>только после пересчета этих позиций</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Собрать лот ЗИП на Пилстик 6ЧН40/46</t>
+          <t>Адресные КП тем, кто просил цену и не получил</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>сотрудница</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>57 позиций, 1222 единицы, искать судно с этим двигателем</t>
+          <t>количества в КП — только по пересчитанным позициям</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Собрать лот ЗИП на VD26/20 и 6NVD26 А3</t>
+          <t>Предложение по светильникам СС328 одним лотом</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>28 позиций, 254 единицы</t>
+          <t>4512 единиц, главный объем</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Связать ремкомплекты сепараторов с самими сепараторами в КП</t>
+          <t>Собрать лот ЗИП на Пилстик 6ЧН40/46</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>кулачки СЦ-1,5 55 шт, СЦ-3 36 шт, ремкомплекты</t>
+          <t>57 позиций, 1222 единицы, искать судно с этим двигателем</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Запрос встречных предложений на склад лотом у 3-5 перекупщиков</t>
+          <t>Собрать лот ЗИП на VD26/20 и 6NVD26 А3</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>цель — узнать цену рынка</t>
+          <t>28 позиций, 254 единицы</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Выставить на Фарпост баллоны кислородные и станки</t>
+          <t>Связать ремкомплекты сепараторов с самими сепараторами в КП</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>их нет в реестре, переписать отдельно</t>
+          <t>кулачки СЦ-1,5 55 шт, СЦ-3 36 шт, ремкомплекты</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>20-23 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
+          <t>Запрос встречных предложений на склад лотом у 3-5 перекупщиков</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>сотрудница + Олеся</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -2300,7 +2300,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>цель — узнать цену рынка</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
@@ -2318,17 +2322,17 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Обмерить, сколько места занимает каждая группа товара</t>
+          <t>Выставить на Фарпост баллоны кислородные и станки</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>новый + Олеся</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2338,7 +2342,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>один день с рулеткой и планом</t>
+          <t>их нет в реестре, переписать отдельно</t>
         </is>
       </c>
     </row>
@@ -2353,22 +2357,22 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>20-23 сен</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Включить склад электрики в обмер и в план вывоза</t>
+          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + Олеся</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2376,11 +2380,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>локация нашлась позже, 117 позиций, 1783 единицы</t>
-        </is>
-      </c>
+      <c r="H49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Узнать рыночную ставку аренды за кв. м в районе</t>
+          <t>Обмерить, сколько места занимает каждая группа товара</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый + Олеся</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>без нее нельзя считать экономику</t>
+          <t>один день с рулеткой и планом</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Выбрать и подготовить место под 40-футовый контейнер</t>
+          <t>Включить склад электрики в обмер и в план вывоза</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>твердое основание, блоки под углы</t>
+          <t>локация нашлась позже, 117 позиций, 1783 единицы</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Воровайка: убрать лебедки с середины двора</t>
+          <t>Узнать рыночную ставку аренды за кв. м в районе</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>чтобы заехал кран</t>
+          <t>без нее нельзя считать экономику</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Вывоз мусора грузовиком с помещения и территории</t>
+          <t>Выбрать и подготовить место под 40-футовый контейнер</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>не сторож по мешку</t>
+          <t>твердое основание, блоки под углы</t>
         </is>
       </c>
     </row>
@@ -2563,98 +2563,102 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
+          <t>Воровайка: убрать лебедки с середины двора</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>чтобы заехал кран</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Вывоз мусора грузовиком с помещения и территории</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>не сторож по мешку</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
           <t>Освободить 20-футовый контейнер вдоль стены</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>пойдет под светильники</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Купить и поставить 40-футовый контейнер</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Полностью освободить здание: товара внутри не остается</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>500 кв. м аренда, 100 кв. м мастерская</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2683,12 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
+          <t>Купить и поставить 40-футовый контейнер</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2692,11 +2696,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>45-55 куб. м, на поддоны, не на землю</t>
-        </is>
-      </c>
+      <c r="H57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="9" t="n">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
+          <t>Полностью освободить здание: товара внутри не остается</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>кран-балка есть на улице, не продавать</t>
+          <t>500 кв. м аренда, 100 кв. м мастерская</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
+          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>часть аренды можно закрывать ремонтом брака</t>
+          <t>45-55 куб. м, на поддоны, не на землю</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
+          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>2844 единицы, опись обязательна</t>
+          <t>кран-балка есть на улице, не продавать</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Маркировать ящики и поддоны по строкам реестра</t>
+          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>иначе не найти проданную позицию</t>
+          <t>часть аренды можно закрывать ремонтом брака</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Освободить гараж от мусора</t>
+          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2892,7 +2892,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>2844 единицы, опись обязательна</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="n">
@@ -2915,7 +2919,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Перенести насосы из фойе после маркировки и фото</t>
+          <t>Маркировать ящики и поддоны по строкам реестра</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2930,7 +2934,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>6 910 000 руб, сначала бирки</t>
+          <t>иначе не найти проданную позицию</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2959,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Покраска будки сторожей</t>
+          <t>Освободить гараж от мусора</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -2991,12 +2995,12 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
+          <t>Перенести насосы из фойе после маркировки и фото</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3006,7 +3010,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>иначе будете платить за арендатора</t>
+          <t>6 910 000 руб, сначала бирки</t>
         </is>
       </c>
     </row>
@@ -3031,12 +3035,12 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
+          <t>Покраска будки сторожей</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3044,11 +3048,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>приложение к договору аренды</t>
-        </is>
-      </c>
+      <c r="H66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
+          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -3084,7 +3084,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>иначе будете платить за арендатора</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Переговоры с Валентином и выход на рынок аренды</t>
+          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -3122,7 +3126,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>не завязываться на одного арендатора</t>
+          <t>приложение к договору аренды</t>
         </is>
       </c>
     </row>
@@ -3142,17 +3146,17 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
+          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -3178,17 +3182,17 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
+          <t>Переговоры с Валентином и выход на рынок аренды</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -3196,7 +3200,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>не завязываться на одного арендатора</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="n">
@@ -3219,12 +3227,12 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Работа по откликам, отгрузки</t>
+          <t>Инвентаризация: пересчитать остальные позиции</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -3232,7 +3240,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>666 позиций, идет параллельно с вывозом</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="n">
@@ -3255,7 +3267,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+          <t>Пересобрать реестр и прайс по фактическим остаткам</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -3270,7 +3282,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>15,9 млн и 76 кв. м площади</t>
+          <t>после этого стоимость склада станет достоверной</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3307,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Составить список на металл и сверить с реестром</t>
+          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
@@ -3310,7 +3322,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>только брак и хлам, подписывает Олеся</t>
+          <t>после пересчета</t>
         </is>
       </c>
     </row>
@@ -3335,176 +3347,176 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
+          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Работа по откликам, отгрузки</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>15,9 млн и 76 кв. м площади</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Составить список на металл и сверить с реестром</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>только брак и хлам, подписывает Олеся</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
           <t>Запросить цены в 2-3 приемках металла отдельно по цветному</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>бронза дороже черного в разы</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Передать показания света: Калинина, Светланская, Фокино</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>ДЭК 18112 и 7182</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>20-25 числа</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Передать показания воды по четырем объектам</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>Водоканал 1008</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>20-25 числа</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Оплатить воду по четырем объектам</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>по счету</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>Оплатить свет</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="n">
@@ -3527,7 +3539,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Принять и оплатить смены сторожей</t>
+          <t>Передать показания света: Калинина, Светланская, Фокино</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -3542,7 +3554,7 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>1280 руб за сутки</t>
+          <t>ДЭК 18112 и 7182</t>
         </is>
       </c>
     </row>
@@ -3557,110 +3569,262 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
+          <t>20-25 числа</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Передать показания воды по четырем объектам</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Водоканал 1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>20-25 числа</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Оплатить воду по четырем объектам</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>по счету</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Оплатить свет</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Принять и оплатить смены сторожей</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>1280 руб за сутки</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
           <t>еженедельно</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>Обход объектов, фотоотчет</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>способ контроля на удаленке</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="D82" s="11" t="inlineStr">
+    <row r="86">
+      <c r="D86" s="11" t="inlineStr">
         <is>
           <t>Сводка</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>Всего задач</t>
         </is>
       </c>
-      <c r="F82" s="12">
-        <f>COUNTA(E5:E80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="F83" s="12">
-        <f>COUNTIF(G5:G80,"Не начато")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="F84" s="12">
-        <f>COUNTIF(G5:G80,"В работе")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>Сделано</t>
-        </is>
-      </c>
-      <c r="F85" s="12">
-        <f>COUNTIF(G5:G80,"Сделано")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>Отменено</t>
-        </is>
-      </c>
       <c r="F86" s="12">
-        <f>COUNTIF(G5:G80,"Отменено")</f>
+        <f>COUNTA(E5:E84)</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="E87" s="12" t="inlineStr">
         <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F87" s="12">
+        <f>COUNTIF(G5:G84,"Не начато")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="F88" s="12">
+        <f>COUNTIF(G5:G84,"В работе")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Сделано</t>
+        </is>
+      </c>
+      <c r="F89" s="12">
+        <f>COUNTIF(G5:G84,"Сделано")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Отменено</t>
+        </is>
+      </c>
+      <c r="F90" s="12">
+        <f>COUNTIF(G5:G84,"Отменено")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="E91" s="12" t="inlineStr">
+        <is>
           <t>Готовность</t>
         </is>
       </c>
-      <c r="F87" s="13">
-        <f>IFERROR(F85/F82,0)</f>
+      <c r="F91" s="13">
+        <f>IFERROR(F89/F86,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H80"/>
+  <autoFilter ref="A4:H84"/>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Сделано,Отменено"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4213,7 +4377,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>камчатский колхоз, НН, Владивосток</t>
+          <t>количества в КП — только по пересчитанным позициям</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4371,7 +4535,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>496 позиций с ценой</t>
+          <t>цифра до инвентаризации, часть товара продана</t>
         </is>
       </c>
     </row>
@@ -4393,228 +4557,245 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr"/>
-      <c r="B9" s="16" t="inlineStr"/>
-      <c r="C9" s="16" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Последняя сверка остатков</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>16.06.2025</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>прошло 15 месяцев, нужна инвентаризация</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Арматура: клапаны и клинкеты</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>288 поз, 3 034 ед</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>40 912 050 руб</t>
-        </is>
-      </c>
+      <c r="A10" s="16" t="inlineStr"/>
+      <c r="B10" s="16" t="inlineStr"/>
+      <c r="C10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Насосное и механическое</t>
+          <t>Арматура: клапаны и клинкеты</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>134 поз, 1 108 ед</t>
+          <t>288 поз, 3 034 ед</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>20 657 248 руб</t>
+          <t>40 912 050 руб</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Электрика</t>
+          <t>Насосное и механическое</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>181 поз, 7 671 ед</t>
+          <t>134 поз, 1 108 ед</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>12 719 930 руб</t>
+          <t>20 657 248 руб</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Корпусная часть: иллюминаторы, двери</t>
+          <t>Электрика</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>30 поз, 195 ед</t>
+          <t>181 поз, 7 671 ед</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>10 055 000 руб</t>
+          <t>12 719 930 руб</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Трубопроводная обвязка</t>
+          <t>Корпусная часть: иллюминаторы, двери</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>38 поз, 244 ед</t>
+          <t>30 поз, 195 ед</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>4 744 800 руб</t>
+          <t>10 055 000 руб</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>Трубопроводная обвязка</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>38 поз, 244 ед</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>4 744 800 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>Прочее: плиты, блокформы, такелаж</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>28 поз, 286 ед</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>3 881 540 руб</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="16" t="inlineStr"/>
-      <c r="C16" s="16" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Где нет цен: склад электрики</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>117 поз, 1 783 ед</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>весь ЗИП двигателей</t>
-        </is>
-      </c>
+      <c r="A17" s="16" t="inlineStr"/>
+      <c r="B17" s="16" t="inlineStr"/>
+      <c r="C17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Где нет цен: склад 3</t>
+          <t>Где нет цен: склад электрики</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>70 поз, 262 ед</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
+          <t>117 поз, 1 783 ед</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>весь ЗИП двигателей</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Где нет цен: перечень ЗИП и насосов</t>
+          <t>Где нет цен: склад 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>32 поз, 224 ед</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>покрывает улицу</t>
-        </is>
-      </c>
+          <t>70 поз, 262 ед</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>Где нет цен: перечень ЗИП и насосов</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>32 поз, 224 ед</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>покрывает улицу</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Где нет цен: склад 2</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>30 поз, 144 ед</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr"/>
-      <c r="B21" s="16" t="inlineStr"/>
-      <c r="C21" s="16" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>80% стоимости дают</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>79 позиций</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>их ведем точечно</t>
-        </is>
-      </c>
+      <c r="A22" s="16" t="inlineStr"/>
+      <c r="B22" s="16" t="inlineStr"/>
+      <c r="C22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Объем всего товара из здания</t>
+          <t>80% стоимости дают</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>155-190 куб. м</t>
+          <t>79 позиций</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>оценка, нужен обмер</t>
+          <t>их ведем точечно</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>Объем всего товара из здания</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>155-190 куб. м</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>оценка, нужен обмер</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>Вместимость 40-фут плюс 20-фут</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>около 100 куб. м</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>разрыв закрывают продажи и навес</t>
         </is>
@@ -6114,7 +6295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6386,12 +6567,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Товар не помещается в два контейнера</t>
+          <t>Остатки недостоверны, часть товара уже продана</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Весь товар из здания — 155-190 куб. м, а 40-футовый и 20-футовый вместе дают 100 куб. м. Разрыв закрывают продажа светильников лотом (50-60 куб. м) и навес во дворе под насосы, сепараторы и плиты (45-55 куб. м). Третий контейнер покупать не надо</t>
+          <t>Учетные файлы сверялись 16.06.2025, прошло 15 месяцев, продажи в них не заносились. Стоимость 92 970 568 руб и все количества под вопросом. До инвентаризации не публикуем объявления, не рассылаем КП с количествами и не называем сумму покупателю. Считаем по ведомости: сначала 79 позиций, дающих 80% стоимости, потом остальные</t>
         </is>
       </c>
     </row>
@@ -6401,12 +6582,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Мастерская мешает арендатору 500 кв. м</t>
+          <t>Товар не помещается в два контейнера</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Сварка, шлифовка и шум рядом с чужим арендатором — источник конфликта. Обсудить до подписания договора, а не после</t>
+          <t>Весь товар из здания — 155-190 куб. м, а 40-футовый и 20-футовый вместе дают 100 куб. м. Разрыв закрывают продажа светильников лотом (50-60 куб. м) и навес во дворе под насосы, сепараторы и плиты (45-55 куб. м). Третий контейнер покупать не надо</t>
         </is>
       </c>
     </row>
@@ -6416,12 +6597,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Объект без ответственного</t>
+          <t>Мастерская мешает арендатору 500 кв. м</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Пока администратора нет, сторож единственный человек на площадке с товаром на 93 млн. Задачи ему ставит Москва напрямую, ежедневное фото территории</t>
+          <t>Сварка, шлифовка и шум рядом с чужим арендатором — источник конфликта. Обсудить до подписания договора, а не после</t>
         </is>
       </c>
     </row>
@@ -6431,12 +6612,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Продажа тянется, аренда не начинается</t>
+          <t>Объект без ответственного</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Отсечка касается здания, а не товара: к дате все вывозится в контейнер, здание сдается, продажа продолжается</t>
+          <t>Пока администратора нет, сторож единственный человек на площадке с товаром на 93 млн. Задачи ему ставит Москва напрямую, ежедневное фото территории</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6627,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Перегруз и просадка контейнера</t>
+          <t>Продажа тянется, аренда не начинается</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Контейнер стационарный, поэтому вес не ограничен транспортной нормой, но нужно твердое основание, поддоны под тяжелое и распределение по длине</t>
+          <t>Отсечка касается здания, а не товара: к дате все вывозится в контейнер, здание сдается, продажа продолжается</t>
         </is>
       </c>
     </row>
@@ -6461,10 +6642,25 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>Перегруз и просадка контейнера</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Контейнер стационарный, поэтому вес не ограничен транспортной нормой, но нужно твердое основание, поддоны под тяжелое и распределение по длине</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>Потеря контактов покупателей</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Журнал обзвона на 40+ компаний уходит вместе с сотрудницей. Передать Олесе со статусами, а не список телефонов</t>
         </is>

--- a/outputs/operations/План_действий_2026-09.xlsx
+++ b/outputs/operations/План_действий_2026-09.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Кто нужен в команду" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Успеть до 23 сентября'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План действий'!$A$4:$H$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Успеть до 23 сентября'!$A$4:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Передача дел'!$A$4:$F$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Склад и здание'!$A$4:$F$23</definedName>
   </definedNames>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1377,22 +1377,22 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>10-16 сен</t>
+          <t>10-11 сен</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>ИНВЕНТАРИЗАЦИЯ: пересчитать 79 позиций, дающих 80% стоимости</t>
+          <t>Список отгрузок с 16.06.2025: что, сколько, кому, когда</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Олеся + новый</t>
+          <t>сотрудница</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>остатки недостоверны, сверка была 15 месяцев назад</t>
+          <t>только она знает, что ушло за 15 месяцев</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>10-16 сен</t>
+          <t>14-15 сен</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Завести правило: каждая отгрузка отмечается в тот же день</t>
+          <t>Пересчитать 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>сотрудница</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>иначе через год остатки снова разойдутся</t>
+          <t>лист «Считать первыми» в ведомости</t>
         </is>
       </c>
     </row>
@@ -1457,22 +1457,22 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10-13 сен</t>
+          <t>16 сен</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Оценить улицу: брашпили Б3 и Б4, лебедки ЛЭ74, ПУ-130, трал</t>
+          <t>Свести пересчет и список отгрузок, объяснить расхождения</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>сотрудница</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>брашпили уже спрашивал покупатель, цены нет</t>
+          <t>продано, списано, не найдено — по каждой позиции</t>
         </is>
       </c>
     </row>
@@ -1497,17 +1497,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>10-13 сен</t>
+          <t>10-16 сен</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Проверить три спорные цифры: СУНДУК, иллюминатор Ф300, РТНД-150</t>
+          <t>Завести правило: каждая отгрузка отмечается в тот же день</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>24 млн под вопросом</t>
+          <t>иначе через год остатки снова разойдутся</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10-14 сен</t>
+          <t>10-13 сен</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Оценить ЗИП двигателей: Пилстик 6ЧН40/46, VD26/20, 6NVD26 А3</t>
+          <t>Оценить улицу: брашпили Б3 и Б4, лебедки ЛЭ74, ПУ-130, трал</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>249 позиций без цены, самое дорогое из неоцененного</t>
+          <t>брашпили уже спрашивал покупатель, цены нет</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>10-14 сен</t>
+          <t>10-13 сен</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Проставить цены на остальные позиции без цены</t>
+          <t>Проверить три спорные цифры: СУНДУК, иллюминатор Ф300, РТНД-150</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>начать с тех, что нужны для КП</t>
+          <t>24 млн под вопросом</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Спросить мастера: взаимозаменяемы ли VD26/20 и 6NVD26 А3</t>
+          <t>Оценить ЗИП двигателей: Пилстик 6ЧН40/46, VD26/20, 6NVD26 А3</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>одна серия SKL 260/200, тогда это один лот</t>
+          <t>249 позиций без цены, самое дорогое из неоцененного</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Свести к одной цене 10 наименований с разной ценой</t>
+          <t>Проставить цены на остальные позиции без цены</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -1680,7 +1680,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>начать с тех, что нужны для КП</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1693,106 +1697,110 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
+          <t>10-14 сен</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Спросить мастера: взаимозаменяемы ли VD26/20 и 6NVD26 А3</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>одна серия SKL 260/200, тогда это один лот</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Неделя 1</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>10-14 сен</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Свести к одной цене 10 наименований с разной ценой</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Неделя 1</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
           <t>13-16 сен</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Разобрать фотоархив по позициям</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>Олеся</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>папка Фото на Google Drive</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Неделя 2</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>сотрудница + новый</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Неделя 2</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Обход Светланской, Фокино, Аксаковской</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>сотрудница + новый</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -1830,7 +1838,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>смена 1280 руб</t>
+          <t>новому передаем уже выверенные остатки</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1863,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+          <t>Обход Светланской, Фокино, Аксаковской</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -1868,11 +1876,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>включая мастера по ремонту арматуры</t>
-        </is>
-      </c>
+      <c r="H36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
@@ -1885,7 +1889,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>20-25 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1895,12 +1899,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Новый сам снимает и передает показания по всем объектам</t>
+          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + новый</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -1910,7 +1914,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>контрольная точка, она рядом и проверяет</t>
+          <t>смена 1280 руб</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1929,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>20-25 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1935,12 +1939,12 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Новый сам оплачивает воду по четырем объектам</t>
+          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>сотрудница + новый</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -1948,7 +1952,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>включая мастера по ремонту арматуры</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
@@ -1961,7 +1969,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>22 сен</t>
+          <t>20-25 сен</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1971,7 +1979,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Контрольный день: новый работает один</t>
+          <t>Новый сам снимает и передает показания по всем объектам</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>она на телефоне</t>
+          <t>контрольная точка, она рядом и проверяет</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2009,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>23 сен</t>
+          <t>20-25 сен</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2011,12 +2019,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Акт приема-передачи, отзыв ключей, смена паролей</t>
+          <t>Новый сам оплачивает воду по четырем объектам</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -2037,22 +2045,22 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>22 сен</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Выложить на Авито и Фарпост первую волну: 24 объявления</t>
+          <t>Контрольный день: новый работает один</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -2062,7 +2070,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>только после пересчета этих позиций</t>
+          <t>она на телефоне</t>
         </is>
       </c>
     </row>
@@ -2077,22 +2085,22 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>23 сен</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Адресные КП тем, кто просил цену и не получил</t>
+          <t>Подписать акт сверки остатков</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>сотрудница</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -2102,7 +2110,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>количества в КП — только по пересчитанным позициям</t>
+          <t>что числилось, что есть по факту, чем объяснено</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2125,22 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>23 сен</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Предложение по светильникам СС328 одним лотом</t>
+          <t>Акт приема-передачи, отзыв ключей, смена паролей</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -2140,11 +2148,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>4512 единиц, главный объем</t>
-        </is>
-      </c>
+      <c r="H43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
@@ -2167,7 +2171,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Собрать лот ЗИП на Пилстик 6ЧН40/46</t>
+          <t>Выложить на Авито и Фарпост первую волну: 24 объявления</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2182,7 +2186,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>57 позиций, 1222 единицы, искать судно с этим двигателем</t>
+          <t>только после пересчета этих позиций</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2211,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Собрать лот ЗИП на VD26/20 и 6NVD26 А3</t>
+          <t>Адресные КП тем, кто просил цену и не получил</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>сотрудница</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2222,7 +2226,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>28 позиций, 254 единицы</t>
+          <t>количества в КП — только по пересчитанным позициям</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2251,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Связать ремкомплекты сепараторов с самими сепараторами в КП</t>
+          <t>Предложение по светильникам СС328 одним лотом</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>кулачки СЦ-1,5 55 шт, СЦ-3 36 шт, ремкомплекты</t>
+          <t>4512 единиц, главный объем</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2291,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Запрос встречных предложений на склад лотом у 3-5 перекупщиков</t>
+          <t>Собрать лот ЗИП на Пилстик 6ЧН40/46</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -2302,7 +2306,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>цель — узнать цену рынка</t>
+          <t>57 позиций, 1222 единицы, искать судно с этим двигателем</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Выставить на Фарпост баллоны кислородные и станки</t>
+          <t>Собрать лот ЗИП на VD26/20 и 6NVD26 А3</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -2342,7 +2346,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>их нет в реестре, переписать отдельно</t>
+          <t>28 позиций, 254 единицы</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2361,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>20-23 сен</t>
+          <t>17-23 сен</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -2367,12 +2371,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
+          <t>Связать ремкомплекты сепараторов с самими сепараторами в КП</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>сотрудница + Олеся</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -2380,7 +2384,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>кулачки СЦ-1,5 55 шт, СЦ-3 36 шт, ремкомплекты</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -2398,17 +2406,17 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Обмерить, сколько места занимает каждая группа товара</t>
+          <t>Запрос встречных предложений на склад лотом у 3-5 перекупщиков</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>новый + Олеся</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>один день с рулеткой и планом</t>
+          <t>цель — узнать цену рынка</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2446,17 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Включить склад электрики в обмер и в план вывоза</t>
+          <t>Выставить на Фарпост баллоны кислородные и станки</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Олеся</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -2458,7 +2466,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>локация нашлась позже, 117 позиций, 1783 единицы</t>
+          <t>их нет в реестре, переписать отдельно</t>
         </is>
       </c>
     </row>
@@ -2473,22 +2481,22 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>17-23 сен</t>
+          <t>20-23 сен</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Здание</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Узнать рыночную ставку аренды за кв. м в районе</t>
+          <t>Совместные звонки: представить Олесю ключевым покупателям</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>сотрудница + Олеся</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -2496,11 +2504,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>без нее нельзя считать экономику</t>
-        </is>
-      </c>
+      <c r="H52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
@@ -2523,12 +2527,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Выбрать и подготовить место под 40-футовый контейнер</t>
+          <t>Обмерить, сколько места занимает каждая группа товара</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>новый + Олеся</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2538,7 +2542,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>твердое основание, блоки под углы</t>
+          <t>один день с рулеткой и планом</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2567,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Воровайка: убрать лебедки с середины двора</t>
+          <t>Включить склад электрики в обмер и в план вывоза</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2578,7 +2582,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>чтобы заехал кран</t>
+          <t>локация нашлась позже, 117 позиций, 1783 единицы</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2607,12 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Вывоз мусора грузовиком с помещения и территории</t>
+          <t>Узнать рыночную ставку аренды за кв. м в районе</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2618,7 +2622,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>не сторож по мешку</t>
+          <t>без нее нельзя считать экономику</t>
         </is>
       </c>
     </row>
@@ -2643,138 +2647,142 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
+          <t>Выбрать и подготовить место под 40-футовый контейнер</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>твердое основание, блоки под углы</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Воровайка: убрать лебедки с середины двора</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>чтобы заехал кран</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Вывоз мусора грузовиком с помещения и территории</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>не сторож по мешку</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Неделя 2</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Здание</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
           <t>Освободить 20-футовый контейнер вдоль стены</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>пойдет под светильники</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Купить и поставить 40-футовый контейнер</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Полностью освободить здание: товара внутри не остается</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>500 кв. м аренда, 100 кв. м мастерская</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Недели 3-4</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>24 сен - 7 окт</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>Здание</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>45-55 куб. м, на поддоны, не на землю</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2807,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
+          <t>Купить и поставить 40-футовый контейнер</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -2812,11 +2820,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>кран-балка есть на улице, не продавать</t>
-        </is>
-      </c>
+      <c r="H60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="9" t="n">
@@ -2839,12 +2843,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
+          <t>Полностью освободить здание: товара внутри не остается</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -2854,7 +2858,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>часть аренды можно закрывать ремонтом брака</t>
+          <t>500 кв. м аренда, 100 кв. м мастерская</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2883,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
+          <t>Поставить навес во дворе под насосы, сепараторы и плиты</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -2894,7 +2898,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>2844 единицы, опись обязательна</t>
+          <t>45-55 куб. м, на поддоны, не на землю</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2923,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Маркировать ящики и поддоны по строкам реестра</t>
+          <t>Проверить мощность 380 В и подъемное оборудование для мастерской</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -2934,7 +2938,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>иначе не найти проданную позицию</t>
+          <t>кран-балка есть на улице, не продавать</t>
         </is>
       </c>
     </row>
@@ -2959,12 +2963,12 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Освободить гараж от мусора</t>
+          <t>Предложить 100 кв. м мастеру, который ремонтирует нашу арматуру</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -2972,7 +2976,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>часть аренды можно закрывать ремонтом брака</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="n">
@@ -2995,7 +3003,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Перенести насосы из фойе после маркировки и фото</t>
+          <t>Загрузить арматуру: тяжелое на поддоны, мелочь в ящики</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -3010,7 +3018,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>6 910 000 руб, сначала бирки</t>
+          <t>2844 единицы, опись обязательна</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3043,7 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Покраска будки сторожей</t>
+          <t>Маркировать ящики и поддоны по строкам реестра</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -3048,7 +3056,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>иначе не найти проданную позицию</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
@@ -3071,12 +3083,12 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
+          <t>Освободить гараж от мусора</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -3084,11 +3096,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>иначе будете платить за арендатора</t>
-        </is>
-      </c>
+      <c r="H67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="9" t="n">
@@ -3111,12 +3119,12 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
+          <t>Перенести насосы из фойе после маркировки и фото</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
@@ -3126,7 +3134,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>приложение к договору аренды</t>
+          <t>6 910 000 руб, сначала бирки</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3159,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
+          <t>Покраска будки сторожей</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -3187,7 +3195,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Переговоры с Валентином и выход на рынок аренды</t>
+          <t>Поставить отдельные счетчики света и воды на 500 кв. м</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -3202,7 +3210,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>не завязываться на одного арендатора</t>
+          <t>иначе будете платить за арендатора</t>
         </is>
       </c>
     </row>
@@ -3222,17 +3230,17 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Инвентаризация: пересчитать остальные позиции</t>
+          <t>Подготовить поэтажный план с выделением 500 и 100 кв. м</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>новый администратор</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -3242,7 +3250,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>666 позиций, идет параллельно с вывозом</t>
+          <t>приложение к договору аренды</t>
         </is>
       </c>
     </row>
@@ -3262,17 +3270,17 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Пересобрать реестр и прайс по фактическим остаткам</t>
+          <t>Разметить территорию: контейнеры, проезд, разгрузка</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -3280,11 +3288,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>после этого стоимость склада станет достоверной</t>
-        </is>
-      </c>
+      <c r="H72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="9" t="n">
@@ -3302,17 +3306,17 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Здание</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
+          <t>Переговоры с Валентином и выход на рынок аренды</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -3322,7 +3326,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>после пересчета</t>
+          <t>не завязываться на одного арендатора</t>
         </is>
       </c>
     </row>
@@ -3342,17 +3346,17 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
+          <t>Пересчитать остальные 666 позиций</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Олеся</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -3360,7 +3364,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>параллельно с укладкой в контейнеры</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="n">
@@ -3378,12 +3386,12 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Работа по откликам, отгрузки</t>
+          <t>Пересобрать реестр и прайс по фактическим остаткам</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -3396,7 +3404,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>после этого стоимость склада станет достоверной</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="n">
@@ -3419,7 +3431,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+          <t>Авито и Фарпост: вторая волна, 40 объявлений</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -3434,7 +3446,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>15,9 млн и 76 кв. м площади</t>
+          <t>после пересчета</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3471,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Составить список на металл и сверить с реестром</t>
+          <t>Авито и Фарпост: третья волна, 12 лотовых объявлений</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -3472,11 +3484,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>только брак и хлам, подписывает Олеся</t>
-        </is>
-      </c>
+      <c r="H77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="9" t="n">
@@ -3499,140 +3507,140 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
+          <t>Работа по откликам, отгрузки</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Продать крупногабарит: насосы, сепараторы, плиты</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>15,9 млн и 76 кв. м площади</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Составить список на металл и сверить с реестром</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Олеся</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>только брак и хлам, подписывает Олеся</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Недели 3-4</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>24 сен - 7 окт</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
           <t>Запросить цены в 2-3 приемках металла отдельно по цветному</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>бронза дороже черного в разы</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Передать показания света: Калинина, Светланская, Фокино</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>ДЭК 18112 и 7182</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>20-25 числа</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>Передать показания воды по четырем объектам</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>новый администратор</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>Водоканал 1008</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>Постоянно</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>20-25 числа</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Объекты</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>Оплатить воду по четырем объектам</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>Москва</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="n">
@@ -3645,7 +3653,7 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>по счету</t>
+          <t>ежемесячно</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -3655,12 +3663,12 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Оплатить свет</t>
+          <t>Передать показания света: Калинина, Светланская, Фокино</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>новый администратор</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -3668,7 +3676,11 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>ДЭК 18112 и 7182</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="n">
@@ -3681,7 +3693,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>ежемесячно</t>
+          <t>20-25 числа</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -3691,7 +3703,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Принять и оплатить смены сторожей</t>
+          <t>Передать показания воды по четырем объектам</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -3706,7 +3718,7 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>1280 руб за сутки</t>
+          <t>Водоканал 1008</t>
         </is>
       </c>
     </row>
@@ -3721,110 +3733,222 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
+          <t>20-25 числа</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Оплатить воду по четырем объектам</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>по счету</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Оплатить свет</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Объекты</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Принять и оплатить смены сторожей</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>новый администратор</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>1280 руб за сутки</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
           <t>еженедельно</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>Объекты</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>Обход объектов, фотоотчет</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>новый администратор</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>способ контроля на удаленке</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="D86" s="11" t="inlineStr">
+    <row r="89">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>Сводка</t>
         </is>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>Всего задач</t>
         </is>
       </c>
-      <c r="F86" s="12">
-        <f>COUNTA(E5:E84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="F87" s="12">
-        <f>COUNTIF(G5:G84,"Не начато")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="F88" s="12">
-        <f>COUNTIF(G5:G84,"В работе")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>Сделано</t>
-        </is>
-      </c>
       <c r="F89" s="12">
-        <f>COUNTIF(G5:G84,"Сделано")</f>
+        <f>COUNTA(E5:E87)</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Отменено</t>
+          <t>Не начато</t>
         </is>
       </c>
       <c r="F90" s="12">
-        <f>COUNTIF(G5:G84,"Отменено")</f>
+        <f>COUNTIF(G5:G87,"Не начато")</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="E91" s="12" t="inlineStr">
         <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="F91" s="12">
+        <f>COUNTIF(G5:G87,"В работе")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Сделано</t>
+        </is>
+      </c>
+      <c r="F92" s="12">
+        <f>COUNTIF(G5:G87,"Сделано")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Отменено</t>
+        </is>
+      </c>
+      <c r="F93" s="12">
+        <f>COUNTIF(G5:G87,"Отменено")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="E94" s="12" t="inlineStr">
+        <is>
           <t>Готовность</t>
         </is>
       </c>
-      <c r="F91" s="13">
-        <f>IFERROR(F89/F86,0)</f>
+      <c r="F94" s="13">
+        <f>IFERROR(F92/F89,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H84"/>
+  <autoFilter ref="A4:H87"/>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Сделано,Отменено"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3838,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4240,22 +4364,22 @@
       <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>10-11 сен</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
+          <t>Список отгрузок с 16.06.2025: что, сколько, кому, когда</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -4263,25 +4387,29 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>только она знает, что ушло за 15 месяцев</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>14-15 сен</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Обход Светланской, Фокино, Аксаковской</t>
+          <t>Пересчитать 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -4289,25 +4417,29 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>лист «Считать первыми» в ведомости</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>17-23 сен</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Люди</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>16 сен</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Остатки</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+          <t>Свести пересчет и список отгрузок, объяснить расхождения</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -4317,7 +4449,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>смена 1280 руб</t>
+          <t>продано, списано, не найдено — по каждой позиции</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4469,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+          <t>Совместный обход Калинина: счетчики, ключи, что где лежит</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -4347,7 +4479,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>включая мастера по ремонту арматуры</t>
+          <t>новому передаем уже выверенные остатки</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4494,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Люди</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Адресные КП тем, кто просил цену и не получил</t>
+          <t>Обход Светланской, Фокино, Аксаковской</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -4375,11 +4507,7 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>количества в КП — только по пересчитанным позициям</t>
-        </is>
-      </c>
+      <c r="F21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -4387,63 +4515,153 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Знакомство со сторожами, порядок приема смены и оплаты</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>смена 1280 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Люди</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Знакомство с подрядчиками и с экономистом ДЭК</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>включая мастера по ремонту арматуры</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>17-23 сен</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Продажи</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Адресные КП тем, кто просил цену и не получил</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>количества в КП — только по пересчитанным позициям</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>20-23 сен</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Продажи</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Совместные звонки: представить Олесю ключевым покупателям</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="12" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="D24" s="12">
-        <f>COUNTA(D5:D22)</f>
+      <c r="D27" s="12">
+        <f>COUNTA(D5:D25)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="12" t="inlineStr">
+    <row r="28">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Сделано</t>
         </is>
       </c>
-      <c r="D25" s="12">
-        <f>COUNTIF(E5:E22,"Сделано")</f>
+      <c r="D28" s="12">
+        <f>COUNTIF(E5:E25,"Сделано")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="12" t="inlineStr">
+    <row r="29">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>Осталось</t>
         </is>
       </c>
-      <c r="D26" s="14">
-        <f>D24-D25</f>
+      <c r="D29" s="14">
+        <f>D27-D28</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F22"/>
+  <autoFilter ref="A4:F25"/>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Сделано,Отменено"</formula1>
     </dataValidation>
   </dataValidations>

--- a/outputs/operations/План_действий_2026-09.xlsx
+++ b/outputs/operations/План_действий_2026-09.xlsx
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>10-11 сен</t>
+          <t>10-15 сен</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Список отгрузок с 16.06.2025: что, сколько, кому, когда</t>
+          <t>Пересчитать 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>только она знает, что ушло за 15 месяцев</t>
+          <t>лист «Считать первыми», начинать с самого дорогого</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>14-15 сен</t>
+          <t>16 сен</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Пересчитать 79 позиций, дающих 80% стоимости</t>
+          <t>Зафиксировать факт: что пересчитано, что нет</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>лист «Считать первыми» в ведомости</t>
+          <t>расхождения не расследуем, склад вели 10 лет</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Свести пересчет и список отгрузок, объяснить расхождения</t>
+          <t>Пересчитать столько позиций сверх 79, сколько успеет</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>продано, списано, не найдено — по каждой позиции</t>
+          <t>по убыванию стоимости</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Подписать акт сверки остатков</t>
+          <t>Подписать акт сверки по пересчитанным позициям</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>что числилось, что есть по факту, чем объяснено</t>
+          <t>фиксируем факт на дату, без поиска причин</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>10-11 сен</t>
+          <t>10-15 сен</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Список отгрузок с 16.06.2025: что, сколько, кому, когда</t>
+          <t>Пересчитать 79 позиций, дающих 80% стоимости</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>только она знает, что ушло за 15 месяцев</t>
+          <t>лист «Считать первыми», начинать с самого дорогого</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>14-15 сен</t>
+          <t>16 сен</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Пересчитать 79 позиций, дающих 80% стоимости</t>
+          <t>Зафиксировать факт: что пересчитано, что нет</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>лист «Считать первыми» в ведомости</t>
+          <t>расхождения не расследуем, склад вели 10 лет</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Свести пересчет и список отгрузок, объяснить расхождения</t>
+          <t>Пересчитать столько позиций сверх 79, сколько успеет</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>продано, списано, не найдено — по каждой позиции</t>
+          <t>по убыванию стоимости</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Учетные файлы сверялись 16.06.2025, прошло 15 месяцев, продажи в них не заносились. Стоимость 92 970 568 руб и все количества под вопросом. До инвентаризации не публикуем объявления, не рассылаем КП с количествами и не называем сумму покупателю. Считаем по ведомости: сначала 79 позиций, дающих 80% стоимости, потом остальные</t>
+          <t>Склад вели десять лет, продажи в файлы не заносились, последняя сверка 16.06.2025. Восстановить историю отгрузок невозможно, поэтому расхождения не расследуем — просто пересчитываем по факту. Стоимость 92 970 568 руб и все количества под вопросом. До инвентаризации не публикуем объявления, не рассылаем КП с количествами и не называем сумму покупателю. Считаем по ведомости: сначала 79 позиций, дающих 80% стоимости, потом остальные</t>
         </is>
       </c>
     </row>
